--- a/ig/DM-MAI-2025/ASS-A22-AASA-ActiviteModaliteForme.xlsx
+++ b/ig/DM-MAI-2025/ASS-A22-AASA-ActiviteModaliteForme.xlsx
@@ -42,7 +42,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>ASS_A22_ASA_ActiviteModaliteForme</t>
+    <t>ASS_A22_AASA_ActiviteModaliteForme</t>
   </si>
   <si>
     <t>Title</t>
